--- a/Icon_Inventory.xlsx
+++ b/Icon_Inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nataliebaldacci/Documents/GitHub/DADU-Homebody-Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_4A891C3950A4D4D6820D88FB707EF564EE0A0861" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72197C26-E802-6F43-AE59-C390501215BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52940" yWindow="900" windowWidth="34560" windowHeight="19820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17280" yWindow="680" windowWidth="17300" windowHeight="9920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Organized Structure" sheetId="1" r:id="rId1"/>
@@ -2836,7 +2836,7 @@
   <dimension ref="A1:E408"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
